--- a/AAII_Financials/Quarterly/KRYPY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KRYPY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="92">
   <si>
     <t>KRYPY</t>
   </si>
@@ -656,68 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -751,8 +774,26 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -786,8 +827,26 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -821,8 +880,26 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,8 +913,14 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -871,8 +954,26 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,8 +1007,26 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -941,8 +1060,26 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -976,8 +1113,26 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -988,8 +1143,14 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1023,8 +1184,26 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1058,8 +1237,26 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1073,8 +1270,14 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1108,8 +1311,26 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1143,8 +1364,26 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1178,8 +1417,26 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1213,8 +1470,26 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1248,8 +1523,26 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1283,8 +1576,26 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1318,8 +1629,26 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1353,8 +1682,26 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1388,8 +1735,26 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1423,8 +1788,26 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1458,8 +1841,26 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1493,8 +1894,26 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1528,8 +1947,26 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1563,8 +2000,26 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1598,8 +2053,26 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1633,48 +2106,84 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1688,8 +2197,14 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1703,323 +2218,491 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1895800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1896300</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1584400</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1585000</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1610200</v>
+      </c>
+      <c r="I41" s="3">
+        <v>1624600</v>
+      </c>
+      <c r="J41" s="3">
         <v>1413500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="K41" s="3">
         <v>1413100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="L41" s="3">
         <v>1535900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="M41" s="3">
         <v>1532500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="N41" s="3">
         <v>1733300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="O41" s="3">
         <v>1729100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="P41" s="3">
         <v>2046100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="Q41" s="3">
         <v>2042600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="R41" s="3">
         <v>1455200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="S41" s="3">
         <v>1445400</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>214100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G42" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>800</v>
+      </c>
+      <c r="K42" s="3">
         <v>214000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="L42" s="3">
         <v>2000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="M42" s="3">
         <v>2000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="N42" s="3">
         <v>166300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="O42" s="3">
         <v>165900</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>151200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="S42" s="3">
         <v>150200</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>543900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>544000</v>
+      </c>
+      <c r="F43" s="3">
+        <v>381700</v>
+      </c>
+      <c r="G43" s="3">
+        <v>381800</v>
+      </c>
+      <c r="H43" s="3">
+        <v>461700</v>
+      </c>
+      <c r="I43" s="3">
+        <v>465800</v>
+      </c>
+      <c r="J43" s="3">
+        <v>287700</v>
+      </c>
+      <c r="K43" s="3">
         <v>74400</v>
       </c>
-      <c r="E43" s="3">
-        <v>74400</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="L43" s="3">
         <v>397500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="M43" s="3">
         <v>396600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="N43" s="3">
         <v>82100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="O43" s="3">
         <v>81900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="P43" s="3">
         <v>348200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="Q43" s="3">
         <v>347600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="R43" s="3">
         <v>89500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="S43" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4722700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>4723900</v>
+      </c>
+      <c r="F44" s="3">
+        <v>4797400</v>
+      </c>
+      <c r="G44" s="3">
+        <v>4799100</v>
+      </c>
+      <c r="H44" s="3">
+        <v>5373700</v>
+      </c>
+      <c r="I44" s="3">
+        <v>5421800</v>
+      </c>
+      <c r="J44" s="3">
         <v>5597700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="K44" s="3">
         <v>5596300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="L44" s="3">
         <v>7139300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="M44" s="3">
         <v>7123200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="N44" s="3">
         <v>5384100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="O44" s="3">
         <v>5371100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="P44" s="3">
         <v>5361000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="Q44" s="3">
         <v>5351800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="R44" s="3">
         <v>5533300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="S44" s="3">
         <v>5496200</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>328000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>328100</v>
+      </c>
+      <c r="F45" s="3">
+        <v>484000</v>
+      </c>
+      <c r="G45" s="3">
+        <v>484100</v>
+      </c>
+      <c r="H45" s="3">
+        <v>203700</v>
+      </c>
+      <c r="I45" s="3">
+        <v>205500</v>
+      </c>
+      <c r="J45" s="3">
         <v>29400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="K45" s="3">
         <v>29300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="L45" s="3">
         <v>49700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="M45" s="3">
         <v>49600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="N45" s="3">
         <v>63200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="O45" s="3">
         <v>63100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="P45" s="3">
         <v>81400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="Q45" s="3">
         <v>81300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="R45" s="3">
         <v>69800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="S45" s="3">
         <v>69300</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7490300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7492300</v>
+      </c>
+      <c r="F46" s="3">
+        <v>7297700</v>
+      </c>
+      <c r="G46" s="3">
+        <v>7300300</v>
+      </c>
+      <c r="H46" s="3">
+        <v>7649200</v>
+      </c>
+      <c r="I46" s="3">
+        <v>7717800</v>
+      </c>
+      <c r="J46" s="3">
         <v>7385500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="K46" s="3">
         <v>7383700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="L46" s="3">
         <v>9124500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="M46" s="3">
         <v>9103900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="N46" s="3">
         <v>7476600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="O46" s="3">
         <v>7458500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="P46" s="3">
         <v>7836700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="Q46" s="3">
         <v>7823200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="R46" s="3">
         <v>7347900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="S46" s="3">
         <v>7298600</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3616500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3617500</v>
+      </c>
+      <c r="F47" s="3">
+        <v>3612500</v>
+      </c>
+      <c r="G47" s="3">
+        <v>3613800</v>
+      </c>
+      <c r="H47" s="3">
+        <v>3532600</v>
+      </c>
+      <c r="I47" s="3">
+        <v>3564300</v>
+      </c>
+      <c r="J47" s="3">
         <v>3527800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="K47" s="3">
         <v>3526900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="L47" s="3">
         <v>3404000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="M47" s="3">
         <v>3396400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="N47" s="3">
         <v>3432500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="O47" s="3">
         <v>3424200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="P47" s="3">
         <v>3569900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="Q47" s="3">
         <v>3563800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="R47" s="3">
         <v>3585000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="S47" s="3">
         <v>3560900</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>953100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>953300</v>
+      </c>
+      <c r="F48" s="3">
+        <v>949600</v>
+      </c>
+      <c r="G48" s="3">
+        <v>949900</v>
+      </c>
+      <c r="H48" s="3">
+        <v>785500</v>
+      </c>
+      <c r="I48" s="3">
+        <v>792500</v>
+      </c>
+      <c r="J48" s="3">
         <v>794700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="K48" s="3">
         <v>794500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="L48" s="3">
         <v>831900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="M48" s="3">
         <v>830000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="N48" s="3">
         <v>768400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="O48" s="3">
         <v>766600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="P48" s="3">
         <v>783100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="Q48" s="3">
         <v>781700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="R48" s="3">
         <v>826900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="S48" s="3">
         <v>821300</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>15700</v>
+      </c>
+      <c r="F49" s="3">
         <v>15800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>15800</v>
-      </c>
-      <c r="F49" s="3">
-        <v>15700</v>
-      </c>
-      <c r="G49" s="3">
-        <v>15700</v>
       </c>
       <c r="H49" s="3">
         <v>15700</v>
       </c>
       <c r="I49" s="3">
-        <v>15700</v>
+        <v>15800</v>
       </c>
       <c r="J49" s="3">
-        <v>15600</v>
+        <v>15800</v>
       </c>
       <c r="K49" s="3">
-        <v>15600</v>
+        <v>15800</v>
       </c>
       <c r="L49" s="3">
         <v>15700</v>
       </c>
       <c r="M49" s="3">
+        <v>15700</v>
+      </c>
+      <c r="N49" s="3">
+        <v>15700</v>
+      </c>
+      <c r="O49" s="3">
+        <v>15700</v>
+      </c>
+      <c r="P49" s="3">
         <v>15600</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>15600</v>
+      </c>
+      <c r="R49" s="3">
+        <v>15700</v>
+      </c>
+      <c r="S49" s="3">
+        <v>15600</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2053,8 +2736,26 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2088,43 +2789,79 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>15558300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>15562400</v>
+      </c>
+      <c r="F52" s="3">
+        <v>14908300</v>
+      </c>
+      <c r="G52" s="3">
+        <v>14913700</v>
+      </c>
+      <c r="H52" s="3">
+        <v>14434900</v>
+      </c>
+      <c r="I52" s="3">
+        <v>14564300</v>
+      </c>
+      <c r="J52" s="3">
         <v>14082500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="K52" s="3">
         <v>14079000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="L52" s="3">
         <v>13468700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="M52" s="3">
         <v>13438300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="N52" s="3">
         <v>14873300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="O52" s="3">
         <v>14837300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="P52" s="3">
         <v>13826500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="Q52" s="3">
         <v>13802700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="R52" s="3">
         <v>13925200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="S52" s="3">
         <v>13831800</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2158,43 +2895,79 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27675500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>27682700</v>
+      </c>
+      <c r="F54" s="3">
+        <v>26891800</v>
+      </c>
+      <c r="G54" s="3">
+        <v>26901500</v>
+      </c>
+      <c r="H54" s="3">
+        <v>26574100</v>
+      </c>
+      <c r="I54" s="3">
+        <v>26812300</v>
+      </c>
+      <c r="J54" s="3">
         <v>25921900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="K54" s="3">
         <v>25915300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="L54" s="3">
         <v>26961800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="M54" s="3">
         <v>26900900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="N54" s="3">
         <v>26681600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="O54" s="3">
         <v>26617000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="P54" s="3">
         <v>26157700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="Q54" s="3">
         <v>26112600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="R54" s="3">
         <v>25839000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="S54" s="3">
         <v>25665700</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2208,8 +2981,14 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2223,183 +3002,279 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>30000</v>
+      </c>
+      <c r="F57" s="3">
+        <v>31100</v>
+      </c>
+      <c r="G57" s="3">
+        <v>31100</v>
+      </c>
+      <c r="H57" s="3">
+        <v>15500</v>
+      </c>
+      <c r="I57" s="3">
+        <v>15700</v>
+      </c>
+      <c r="J57" s="3">
         <v>77400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="K57" s="3">
         <v>77400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="L57" s="3">
         <v>889500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="M57" s="3">
         <v>887400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="N57" s="3">
         <v>29300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="O57" s="3">
         <v>29200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="P57" s="3">
         <v>15400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="Q57" s="3">
         <v>15300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="R57" s="3">
         <v>43100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="S57" s="3">
         <v>42800</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1102400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1102700</v>
+      </c>
+      <c r="F58" s="3">
+        <v>834300</v>
+      </c>
+      <c r="G58" s="3">
+        <v>834600</v>
+      </c>
+      <c r="H58" s="3">
+        <v>750300</v>
+      </c>
+      <c r="I58" s="3">
+        <v>757100</v>
+      </c>
+      <c r="J58" s="3">
         <v>1270600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="K58" s="3">
         <v>1270200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="L58" s="3">
         <v>1033700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="M58" s="3">
         <v>1031300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="N58" s="3">
         <v>869700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="O58" s="3">
         <v>867600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="P58" s="3">
         <v>1463600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="Q58" s="3">
         <v>1461000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="R58" s="3">
         <v>787700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="S58" s="3">
         <v>782500</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3243900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3244700</v>
+      </c>
+      <c r="F59" s="3">
+        <v>2630700</v>
+      </c>
+      <c r="G59" s="3">
+        <v>2631700</v>
+      </c>
+      <c r="H59" s="3">
+        <v>2262100</v>
+      </c>
+      <c r="I59" s="3">
+        <v>2282300</v>
+      </c>
+      <c r="J59" s="3">
         <v>1540400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="K59" s="3">
         <v>1540000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="L59" s="3">
         <v>1436000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="M59" s="3">
         <v>1432700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="N59" s="3">
         <v>2409500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="O59" s="3">
         <v>2403700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="P59" s="3">
         <v>2051600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="Q59" s="3">
         <v>2048000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="R59" s="3">
         <v>1669700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="S59" s="3">
         <v>1658500</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4376300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4377400</v>
+      </c>
+      <c r="F60" s="3">
+        <v>3496100</v>
+      </c>
+      <c r="G60" s="3">
+        <v>3497400</v>
+      </c>
+      <c r="H60" s="3">
+        <v>3027900</v>
+      </c>
+      <c r="I60" s="3">
+        <v>3055100</v>
+      </c>
+      <c r="J60" s="3">
         <v>2888300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="K60" s="3">
         <v>2887600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="L60" s="3">
         <v>3359100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="M60" s="3">
         <v>3351500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="N60" s="3">
         <v>3308600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="O60" s="3">
         <v>3300500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="P60" s="3">
         <v>3530500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="Q60" s="3">
         <v>3524400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="R60" s="3">
         <v>2500500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="S60" s="3">
         <v>2483700</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6408700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6410400</v>
+      </c>
+      <c r="F61" s="3">
+        <v>6664800</v>
+      </c>
+      <c r="G61" s="3">
+        <v>6667200</v>
+      </c>
+      <c r="H61" s="3">
+        <v>7119000</v>
+      </c>
+      <c r="I61" s="3">
+        <v>7182900</v>
+      </c>
+      <c r="J61" s="3">
         <v>6696200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="K61" s="3">
         <v>6694600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="L61" s="3">
         <v>7099600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="M61" s="3">
         <v>7083600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="N61" s="3">
         <v>6535200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="O61" s="3">
         <v>6519400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="P61" s="3">
         <v>6134800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="Q61" s="3">
         <v>6124200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="R61" s="3">
         <v>6386900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="S61" s="3">
         <v>6344100</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2433,8 +3308,26 @@
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2468,8 +3361,26 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2503,8 +3414,26 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2538,43 +3467,79 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12260900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>12264100</v>
+      </c>
+      <c r="F66" s="3">
+        <v>11578400</v>
+      </c>
+      <c r="G66" s="3">
+        <v>11582600</v>
+      </c>
+      <c r="H66" s="3">
+        <v>11520100</v>
+      </c>
+      <c r="I66" s="3">
+        <v>11623400</v>
+      </c>
+      <c r="J66" s="3">
         <v>10904500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="K66" s="3">
         <v>10901800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="L66" s="3">
         <v>11797700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="M66" s="3">
         <v>11771000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="N66" s="3">
         <v>11172300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="O66" s="3">
         <v>11145200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="P66" s="3">
         <v>10910800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="Q66" s="3">
         <v>10892000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="R66" s="3">
         <v>10130800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="S66" s="3">
         <v>10062800</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2588,8 +3553,14 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2623,8 +3594,26 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2658,8 +3647,26 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2693,8 +3700,26 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2728,43 +3753,79 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10954300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>10957200</v>
+      </c>
+      <c r="F72" s="3">
+        <v>11270300</v>
+      </c>
+      <c r="G72" s="3">
+        <v>11274400</v>
+      </c>
+      <c r="H72" s="3">
+        <v>11089600</v>
+      </c>
+      <c r="I72" s="3">
+        <v>11189100</v>
+      </c>
+      <c r="J72" s="3">
         <v>11442500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="K72" s="3">
         <v>11439700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="L72" s="3">
         <v>11344500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="M72" s="3">
         <v>11318800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="N72" s="3">
         <v>11475900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="O72" s="3">
         <v>11448100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="P72" s="3">
         <v>11214100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="Q72" s="3">
         <v>11194800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="R72" s="3">
         <v>11337500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="S72" s="3">
         <v>11261400</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2798,8 +3859,26 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2833,8 +3912,26 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2868,43 +3965,79 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13591900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>13595400</v>
+      </c>
+      <c r="F76" s="3">
+        <v>13525100</v>
+      </c>
+      <c r="G76" s="3">
+        <v>13530000</v>
+      </c>
+      <c r="H76" s="3">
+        <v>13282100</v>
+      </c>
+      <c r="I76" s="3">
+        <v>13401200</v>
+      </c>
+      <c r="J76" s="3">
         <v>13300400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="K76" s="3">
         <v>13297100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="L76" s="3">
         <v>13429800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="M76" s="3">
         <v>13399400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="N76" s="3">
         <v>13730000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="O76" s="3">
         <v>13696800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="P76" s="3">
         <v>13556400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="Q76" s="3">
         <v>13533100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="R76" s="3">
         <v>13951900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="S76" s="3">
         <v>13858300</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2938,48 +4071,84 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3013,8 +4182,26 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3028,43 +4215,67 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>13900</v>
+      </c>
+      <c r="F83" s="3">
+        <v>14400</v>
+      </c>
+      <c r="G83" s="3">
+        <v>14400</v>
+      </c>
+      <c r="H83" s="3">
+        <v>13600</v>
+      </c>
+      <c r="I83" s="3">
+        <v>13600</v>
+      </c>
+      <c r="J83" s="3">
         <v>13700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="K83" s="3">
         <v>13700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="L83" s="3">
         <v>14700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="M83" s="3">
         <v>14600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="N83" s="3">
         <v>14900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="O83" s="3">
         <v>14800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="P83" s="3">
         <v>16000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="Q83" s="3">
         <v>16000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="R83" s="3">
         <v>16800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="S83" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3098,8 +4309,26 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3133,8 +4362,26 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3168,8 +4415,26 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3203,8 +4468,26 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3238,43 +4521,79 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>180000</v>
+      </c>
+      <c r="F89" s="3">
+        <v>494300</v>
+      </c>
+      <c r="G89" s="3">
+        <v>494400</v>
+      </c>
+      <c r="H89" s="3">
+        <v>414000</v>
+      </c>
+      <c r="I89" s="3">
+        <v>417700</v>
+      </c>
+      <c r="J89" s="3">
         <v>173800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="K89" s="3">
         <v>173800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="L89" s="3">
         <v>-98300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="M89" s="3">
         <v>-98100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="N89" s="3">
         <v>200000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="O89" s="3">
         <v>199600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="P89" s="3">
         <v>118100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="Q89" s="3">
         <v>117900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="R89" s="3">
         <v>-13500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="S89" s="3">
         <v>-13400</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3288,43 +4607,67 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J91" s="3">
         <v>-5300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="K91" s="3">
         <v>-5300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="L91" s="3">
         <v>-1700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="M91" s="3">
         <v>-1700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="N91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="O91" s="3">
         <v>-1800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="P91" s="3">
         <v>-2400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="Q91" s="3">
         <v>-2400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="R91" s="3">
         <v>-2100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="S91" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3358,8 +4701,26 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3393,43 +4754,79 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>105100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>105100</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-199100</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-199100</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-187800</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-189500</v>
+      </c>
+      <c r="J94" s="3">
         <v>-79900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="K94" s="3">
         <v>-79900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="L94" s="3">
         <v>-266200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="M94" s="3">
         <v>-265600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="N94" s="3">
         <v>-215000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="O94" s="3">
         <v>-214500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="P94" s="3">
         <v>57700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="Q94" s="3">
         <v>57600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="R94" s="3">
         <v>99900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="S94" s="3">
         <v>99200</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3443,43 +4840,67 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>37400</v>
+        <v>87900</v>
       </c>
       <c r="E96" s="3">
+        <v>87900</v>
+      </c>
+      <c r="F96" s="3">
         <v>37300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
+        <v>37300</v>
+      </c>
+      <c r="H96" s="3">
+        <v>87800</v>
+      </c>
+      <c r="I96" s="3">
+        <v>88600</v>
+      </c>
+      <c r="J96" s="3">
+        <v>37300</v>
+      </c>
+      <c r="K96" s="3">
+        <v>37300</v>
+      </c>
+      <c r="L96" s="3">
         <v>88300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="M96" s="3">
         <v>88100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="N96" s="3">
         <v>37100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="O96" s="3">
         <v>37000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="P96" s="3">
         <v>88000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="Q96" s="3">
         <v>87800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="R96" s="3">
         <v>37200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="S96" s="3">
         <v>37000</v>
       </c>
     </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3513,8 +4934,26 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3548,8 +4987,26 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3583,109 +5040,181 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-142400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-142400</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-328300</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-328400</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-137100</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-138400</v>
+      </c>
+      <c r="J100" s="3">
         <v>-150500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="K100" s="3">
         <v>-150500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="L100" s="3">
         <v>283500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="M100" s="3">
         <v>282800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="N100" s="3">
         <v>-150600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="O100" s="3">
         <v>-150200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="P100" s="3">
         <v>147200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="Q100" s="3">
         <v>146900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="R100" s="3">
         <v>-358300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="S100" s="3">
         <v>-355900</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E101" s="3">
+        <v>18000</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="J101" s="3">
         <v>6000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="K101" s="3">
         <v>6000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="L101" s="3">
         <v>-24000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="M101" s="3">
         <v>-24000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="N101" s="3">
         <v>-36600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="O101" s="3">
         <v>-36300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="P101" s="3">
         <v>-40000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="Q101" s="3">
         <v>-40100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="R101" s="3">
         <v>18400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="S101" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>161800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>161900</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="H102" s="3">
+        <v>106900</v>
+      </c>
+      <c r="I102" s="3">
+        <v>107800</v>
+      </c>
+      <c r="J102" s="3">
         <v>-65000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="K102" s="3">
         <v>-65000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="L102" s="3">
         <v>-99100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="M102" s="3">
         <v>-98900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="N102" s="3">
         <v>-159500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="O102" s="3">
         <v>-159100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="P102" s="3">
         <v>299000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="Q102" s="3">
         <v>298500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="R102" s="3">
         <v>-308500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="S102" s="3">
         <v>-306400</v>
       </c>
     </row>
